--- a/샘플/샘플_입력_테스트_21명.xlsx
+++ b/샘플/샘플_입력_테스트_21명.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>김호순</t>
+          <t>김효순</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -1507,11 +1507,7 @@
       </c>
       <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n"/>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>26.7.25 대진표엔 '김효순'으로 표기 — 동일인이면 그대로</t>
-        </is>
-      </c>
+      <c r="K4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">

--- a/샘플/샘플_입력_테스트_21명.xlsx
+++ b/샘플/샘플_입력_테스트_21명.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A128"/>
+  <dimension ref="A1:A142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -642,673 +642,771 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>• 메모: 자유 기재 (선택, 알고리즘에 영향 없음)</t>
+          <t>• 혼복희망: 그중 혼복(남녀 섞인 복식)으로 뛰고 싶은 게임 수 (정수, 선택)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 예: '혼복으로 2게임은 하고 싶어요' → 2 입력</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>■ 2. 코트 시트 작성법</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 비워 두는 것이 기본입니다. 원칙은 남복/여복이라 혼복은 0판일 수 있습니다</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>• 기본값: A코트(08:00-12:00), B코트(08:00-12:00), C코트(07:00-09:00)</t>
+          <t xml:space="preserve">    - 적은 사람이 있으면 그만큼 혼복 판을 만들고 그 자리에 그 사람을 넣습니다</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>• 메모: 자유 기재 (선택, 알고리즘에 영향 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>■ 2. 코트 시트 작성법</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>• 기본값: A코트=1번(07:00-12:00), B코트=2번(07:00-12:00), C코트=3번(07:00-09:00)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 2026.8.8부터 운동시간 07:00~12:00 (3번 코트는 07:00~09:00 그대로)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
           <t>• 코트가 더 있거나 운영시간이 다르면 행을 수정/추가하세요</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>• 시간은 30분 단위, 시작 &lt; 종료</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>• 사용하지 않는 행은 빈 칸으로 두면 됩니다</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>■ 3. 자동 배정 규칙 (알고리즘 동작 원리)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>[A] 기본 단위</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>• 1게임 = 30분</t>
+          <t>• 사용하지 않는 행은 빈 칸으로 두면 됩니다</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>• 한 사람은 같은 시간 슬롯에 두 개 코트 동시 출전 불가</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>• 각자 본인 IN~OUT 범위 안의 슬롯에만 배정됨</t>
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>■ 3. 자동 배정 규칙 (알고리즘 동작 원리)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr"/>
+      <c r="A38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>[B] 복식 종류 우선순위</t>
+          <t>[A] 기본 단위</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>• 남자복식·여자복식이 원칙 — 만들 수 있으면 항상 이쪽이 먼저</t>
+          <t>• 1게임 = 30분</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>• 다만 여자가 6명 이하면 혼합복식을 기본으로 1~2판 넣습니다</t>
+          <t>• 한 사람은 같은 시간 슬롯에 두 개 코트 동시 출전 불가</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (여자복식만 돌리면 늘 같은 사람끼리 붙게 되므로)</t>
+          <t>• 각자 본인 IN~OUT 범위 안의 슬롯에만 배정됨</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>• 그 밖에 혼합복식이 늘어나는 경우 — 단성 복식을 더 짜도 '쓸 만한 대진'이</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  안 나올 때입니다. 쓸 만하다 = ① 같은 짝이 처음이고 ② 같은 4명이 다시</t>
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>[B] 복식 종류 우선순위</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  붙는 게 아니고 ③ 두 팀 구력 합 차이가 허용치 이내.</t>
+          <t>• 남자복식·여자복식이 원칙 — 만들 수 있으면 항상 이쪽이 먼저</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">      허용치는 출전 4명이 모두 구력 10년 미만이면 3, 10년 이상인 분이 끼면 4입니다.</t>
+          <t>• 다만 여자가 6명 이하면 혼합복식을 기본으로 1~2판 넣습니다</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    예) 방미라(3)+노남숙(3)=6 vs 서명숙(5)+정정희(5)=10 은 4 차이인데</t>
+          <t xml:space="preserve">    (여자복식만 돌리면 늘 같은 사람끼리 붙게 되므로)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">        전원 10년 미만이라 허용치가 3 → 이 조합은 만들지 않습니다.</t>
+          <t>• 그 밖에 혼합복식이 늘어나는 경우 — 단성 복식을 더 짜도 '쓸 만한 대진'이</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">        쓸 만한 조합이 모자라면 그만큼 혼합복식으로 채웁니다.</t>
+          <t xml:space="preserve">  안 나올 때입니다. 쓸 만하다 = ① 같은 짝이 처음이고 ② 같은 편 구성으로 다시</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>• 남자 또는 여자가 4명이 안 되면 단성 복식 자체가 불가능 → 혼합복식만 나옵니다</t>
+          <t xml:space="preserve">  붙는 게 아니고 ③ 두 팀 구력 합 차이가 허용치 이내.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>• 혼합복식 규칙: 같은 팀의 남자 구력 ≥ 여자 구력</t>
+          <t xml:space="preserve">      허용치는 출전 4명이 모두 구력 10년 미만이면 3, 10년 이상인 분이 끼면 4입니다.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (남자가 같은 팀 여자보다 경력이 같거나 더 많아야 함)</t>
+          <t xml:space="preserve">    예) 방미라(3)+노남숙(3)=6 vs 서명숙(5)+정정희(5)=10 은 4 차이인데</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>• 남자 게스트는 혼합복식보다 남자복식 위주로 배정합니다</t>
+          <t xml:space="preserve">        전원 10년 미만이라 허용치가 3 → 이 조합은 만들지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (혼합복식의 남자 자리는 가급적 정회원이 맡음 — 여자 게스트는 혼합복식 가능)</t>
+          <t xml:space="preserve">        쓸 만한 조합이 모자라면 그만큼 혼합복식으로 채웁니다.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr"/>
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>• 남자 또는 여자가 4명이 안 되면 단성 복식 자체가 불가능 → 혼합복식만 나옵니다</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>[C] 코트별 우선 배정</t>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>• 혼합복식 규칙: 같은 팀의 남자 구력 ≥ 여자 구력</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>• A코트: 여자복식 + 혼합복식 우선</t>
+          <t xml:space="preserve">    (남자가 같은 팀 여자보다 경력이 같거나 더 많아야 함)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>• B코트: 남자복식 우선</t>
+          <t>• 남자 게스트는 혼합복식보다 남자복식 위주로 배정합니다</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>• C코트: 무관 (균등 배분)</t>
+          <t xml:space="preserve">    (혼합복식의 남자 자리는 가급적 정회원이 맡음 — 여자 게스트는 혼합복식 가능)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ※ 단, 인원 부족 시 위 우선순위는 양보될 수 있음</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr"/>
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>[C] 코트별 우선 배정</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>[D] 시간 제약</t>
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>• A코트: 여자복식 + 혼합복식 우선</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>• 여성 참가자는 가급적 07:30 이후 슬롯에 배정</t>
+          <t>• B코트: 남자복식 우선</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (IN시간이 더 우선 — 7시 IN이면 7시부터 가능)</t>
+          <t>• C코트: 무관 (균등 배분)</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr"/>
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ※ 단, 인원 부족 시 위 우선순위는 양보될 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="inlineStr">
-        <is>
-          <t>[E] 팀 매칭 (재미와 균형)</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>• 두 팀의 합산 구력이 비슷하도록 매칭 (예: 5+7=12 vs 6+6=12)</t>
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>[D] 시간 제약</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>• 합산 구력 차이가 허용치(전원 10년 미만 3 / 10년 이상 포함 4)를 넘으면 강하게 회피 —</t>
+          <t>• 각자 IN~OUT 시간 안에서만 배정 (성별에 따른 시간대 제한은 없음)</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  그렇게 될 바에는 다른 조합이나 혼합복식으로 돌립니다</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>• 한 번 같은 팀이었던 페어는 가능한 한 다시 같은 팀이 안 되게</t>
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>[E] 팀 매칭 (재미와 균형)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>• 같은 4명이 다시 붙는 것을 강하게 회피 — 상대편까지 그대로든, 편만 바꾸든</t>
+          <t>• 두 팀의 합산 구력이 비슷하도록 매칭 (예: 5+7=12 vs 6+6=12)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (그렇게 될 바에는 혼합복식으로 돌립니다)</t>
+          <t>• 합산 구력 차이가 허용치(전원 10년 미만 3 / 10년 이상 포함 4)를 넘으면 강하게 회피 —</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>• 한 팀에 정회원+게스트 혼합 약하게 권장 (강제 아님)</t>
+          <t xml:space="preserve">  그렇게 될 바에는 다른 조합이나 혼합복식으로 돌립니다</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr"/>
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>• 한 번 같은 팀이었던 페어는 가능한 한 다시 같은 팀이 안 되게</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="inlineStr">
-        <is>
-          <t>[F] 게임수 균형</t>
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>• 같은 4명이 다시 붙는 것을 강하게 회피 — 상대편까지 그대로든, 편만 바꾸든</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>• 가용 시간이 비슷한 사람들끼리 게임수 격차 ±1~2 이내 목표</t>
+          <t xml:space="preserve">  (그렇게 될 바에는 혼합복식으로 돌립니다)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>• 남녀 평균 게임수가 한쪽만 낮아지지 않게 별도로 확인</t>
+          <t xml:space="preserve">    ※ 예외: 그 성별로 만들 4명 조합이 하나뿐일 때(예: 여자가 정확히 4명)는</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (여자 인원이 적으면 복식 특성상 '4명 통째로'만 늘어나 손해 보기 쉬움)</t>
+          <t xml:space="preserve">       편을 바꾸면 짝도 상대도 매번 새로우므로 여자복식 3판까지 그대로 만듭니다.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>• 일찍 와서 늦게 가는 사람은 자연스럽게 더 많이 배정</t>
+          <t xml:space="preserve">       (여기서 막으면 여자복식이 1판에서 끝나고 나머지가 전부 혼합복식이 됩니다)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>• 늦게 오거나 일찍 가는 사람은 그만큼 적게 배정</t>
+          <t>• 한 팀에 정회원+게스트 혼합 약하게 권장 (강제 아님)</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>• 전체 격차는 4 이하 권장 (가용 인원이 빠듯하면 더 클 수 있음)</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr"/>
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>[F] 게임수 균형</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="inlineStr">
-        <is>
-          <t>[G] 쉬는 텀 · 끝나는 시간</t>
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>• 가용 시간이 비슷한 사람들끼리 게임수 격차 ±1~2 이내 목표</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>• 경기 사이에 1시간 이상 쉬었다 다시 나오는 일을 최우선으로 줄임</t>
+          <t>• 남녀 평균 게임수가 한쪽만 낮아지지 않게 별도로 확인</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (30분 쉬고 다음 경기가 기본 리듬. 2게임 연속은 정상)</t>
+          <t xml:space="preserve">  (여자 인원이 적으면 복식 특성상 '4명 통째로'만 늘어나 손해 보기 쉬움)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>• 한 사람이 3슬롯(1.5시간) 연속 출전은 가능한 한 회피</t>
+          <t>• 일찍 와서 늦게 가는 사람은 자연스럽게 더 많이 배정</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>• 도착(IN) 후 첫 경기까지 오래 기다리지 않게 배정</t>
+          <t>• 늦게 오거나 일찍 가는 사람은 그만큼 적게 배정</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>• 노는 시간이 한 사람에게 몰리지 않게 고르게 분산</t>
+          <t>• 전체 격차는 4 이하 권장 (가용 인원이 빠듯하면 더 클 수 있음)</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  → 결과적으로 일찍 온 사람이 일찍 끝나고, 늦게 온 사람이 뒤쪽을 맡음</t>
-        </is>
-      </c>
+      <c r="A89" s="2" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (가용 인원이 코트수×4보다 훨씬 많으면 공백이 구조적으로 불가피)</t>
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>[G] 쉬는 텀 · 끝나는 시간</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr"/>
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>• 경기 사이에 1시간 이상 쉬었다 다시 나오는 일을 최우선으로 줄임</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="inlineStr">
-        <is>
-          <t>[H] 개인별 최소·최대 게임수</t>
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (30분 쉬고 다음 경기가 기본 리듬. 2게임 연속은 정상)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>• 최소게임수 칸에 정수 입력 시 적어도 그 수 이상 배정 (어기지 않는 규칙)</t>
+          <t>• 한 사람이 3슬롯(1.5시간) 연속 출전은 금지 — 2게임 연속했으면 반드시 한 번 쉼</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - 본인 가용 슬롯 수를 넘는 값은 슬롯 수까지만 보장</t>
+          <t>• 도착(IN) 후 첫 경기까지 오래 기다리지 않게 배정</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    - 여러 명의 최소게임수 합이 전체 자리보다 크면 다 지킬 수 없음 (경고 표시)</t>
+          <t>• 노는 시간이 한 사람에게 몰리지 않게 고르게 분산</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>• 최대게임수 칸에 정수 입력 시 정확히 그 수 이하로 배정 (hard 제약)</t>
+          <t xml:space="preserve">  → 결과적으로 일찍 온 사람이 일찍 끝나고, 늦게 온 사람이 뒤쪽을 맡음</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>• 빈 칸이면 IN~OUT 범위 안에서 균형 배정</t>
+          <t xml:space="preserve">  (가용 인원이 코트수×4보다 훨씬 많으면 공백이 구조적으로 불가피)</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr"/>
+      <c r="A98" s="2" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>[I] 교류전 (클럽 대항)</t>
+          <t>[H] 개인별 최소·최대 게임수</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>• '클럽' 칸에 둘 이상의 클럽명이 있으면 교류전 모드 자동 작동</t>
+          <t>• 최소게임수 칸에 정수 입력 시 적어도 그 수 이상 배정 (어기지 않는 규칙)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>• 한 팀(복식 2명)은 반드시 같은 클럽끼리 구성 (hard 제약)</t>
+          <t xml:space="preserve">    - 본인 가용 슬롯 수를 넘는 값은 슬롯 수까지만 보장</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>• 모든 경기는 반드시 상대 클럽과 (같은 클럽끼리는 절대 안 붙음, hard)</t>
+          <t xml:space="preserve">    - 여러 명의 최소게임수 합이 전체 자리보다 크면 다 지킬 수 없음 (경고 표시)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>• 게임수 균형은 '각 클럽 내부'에서만 — 두 클럽 인원이 다르면 클럽 간 평균은 다를 수 있음</t>
+          <t>• 최대게임수 칸에 정수 입력 시 정확히 그 수 이하로 배정 (hard 제약)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>• 클럽 칸이 모두 비었거나 한 종류면 평소대로 동작 (영향 없음)</t>
+          <t>• 빈 칸이면 IN~OUT 범위 안에서 균형 배정</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>• 주의: 상대 클럽 인원이 부족한 슬롯에선 남는 사람이 쉬고 그 코트는 공석이 될 수 있음</t>
+          <t>• 혼복희망 칸에 정수 입력 시 그만큼 혼복 판을 열고 그 사람을 그 자리에 배정 (소프트)</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr"/>
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 아무도 안 적으면 지금까지와 동일 — 남복/여복 우선 원칙 그대로</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="inlineStr">
-        <is>
-          <t>■ 4. 알고리즘이 회피 못 하는 입력 구조 (참고)</t>
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    - 남자 게스트도 혼복희망을 적으면 '남복 위주' 규칙에서 본인만 예외가 됩니다</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>• 여자 인원이 4명 미만 → 여자복식 불가, 혼복만 가능</t>
+          <t xml:space="preserve">    - 구력·공백·최소게임수 같은 더 강한 규칙에 밀리면 못 채울 수 있음 (검토 보고에 표시)</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>• 남자 인원이 4명 미만 → 남자복식 불가, 혼복만 가능</t>
-        </is>
-      </c>
+      <c r="A109" s="2" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>• 여자 최고 구력 &gt; 남자 최고 구력 → 혼복 시 일부 규칙 위반 불가피</t>
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>[I] 교류전 (클럽 대항)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (예: 김승회 10년 vs 남자 최고 8년)</t>
+          <t>• '클럽' 칸에 둘 이상의 클럽명이 있으면 교류전 모드 자동 작동</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>• 가용 인원 = 코트수×4 → 휴식 자리 없어 연속 출전 발생</t>
+          <t>• 한 팀(복식 2명)은 반드시 같은 클럽끼리 구성 (hard 제약)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>• 특정 슬롯에 가용 인원 4명 미만 → 그 코트는 자동 공석</t>
+          <t>• 모든 경기는 반드시 상대 클럽과 (같은 클럽끼리는 절대 안 붙음, hard)</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr"/>
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>• 게임수 균형은 '각 클럽 내부'에서만 — 두 클럽 인원이 다르면 클럽 간 평균은 다를 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="inlineStr">
-        <is>
-          <t>■ 5. 결과 생성 방법</t>
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>• 클럽 칸이 모두 비었거나 한 종류면 평소대로 동작 (영향 없음)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>• Windows 명령창(또는 PowerShell)에서:</t>
+          <t>• 주의: 상대 클럽 인원이 부족한 슬롯에선 남는 사람이 쉬고 그 코트는 공석이 될 수 있음</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     python 대진표_생성.py --date "26.5.30"</t>
-        </is>
-      </c>
+      <c r="A117" s="2" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>• 또는 대진표_생성.bat 더블클릭</t>
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>■ 4. 알고리즘이 회피 못 하는 입력 구조 (참고)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>• 결과 파일: 출력/테니스_대진표_&lt;날짜&gt;.xlsx</t>
+          <t>• 여자 인원이 4명 미만 → 여자복식 불가, 혼복만 가능</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr"/>
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>• 남자 인원이 4명 미만 → 남자복식 불가, 혼복만 가능</t>
+        </is>
+      </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="inlineStr">
-        <is>
-          <t>■ 6. 다시 생성하고 싶을 때</t>
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>• 여자 최고 구력 &gt; 남자 최고 구력 → 혼복 시 일부 규칙 위반 불가피</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>• 같은 입력으로 다른 패턴 원하면 --seed 99 (또는 다른 숫자)</t>
+          <t xml:space="preserve">    (예: 김승회 10년 vs 남자 최고 8년)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>• 입력 양식 수정 후 다시 실행하면 새로 생성</t>
+          <t>• 가용 인원 = 코트수×4 → 휴식 자리 없어 연속 출전 발생</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr"/>
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>• 특정 슬롯에 가용 인원 4명 미만 → 그 코트는 자동 공석</t>
+        </is>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="inlineStr">
-        <is>
-          <t>■ 7. 파일 위치</t>
-        </is>
-      </c>
+      <c r="A125" s="2" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>• 입력 양식: 입력/테니스_입력양식.xlsx</t>
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>■ 5. 결과 생성 방법</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>• 결과 파일: 출력/테니스_대진표_&lt;YYMMDD&gt;.xlsx</t>
+          <t>• Windows 명령창(또는 PowerShell)에서:</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     python 대진표_생성.py --date "26.5.30"</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>• 또는 대진표_생성.bat 더블클릭</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>• 결과 파일: 출력/테니스_대진표_&lt;날짜&gt;.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>• 채운 양식을 먼저 검사만 하려면 (대진표 생성 안 함):</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     python 대진표_생성.py --check   (또는 대진표_생성.bat 실행 후 C 입력)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - 오류·경고, 인원·자리 요약, 최소/최대게임수 지정 현황을 보여줍니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>■ 6. 다시 생성하고 싶을 때</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>• 같은 입력으로 다른 패턴 원하면 --seed 99 (또는 다른 숫자)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>• 입력 양식 수정 후 다시 실행하면 새로 생성</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>■ 7. 파일 위치</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>• 입력 양식: 입력/테니스_입력양식.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>• 결과 파일: 출력/테니스_대진표_&lt;YYMMDD&gt;.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>• 샘플/참고: 샘플/  (이미지·예시 데이터)</t>
         </is>
@@ -1325,7 +1423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1338,7 +1436,8 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1394,6 +1493,11 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>혼복희망</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
           <t>메모</t>
         </is>
       </c>
@@ -1434,6 +1538,7 @@
       <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -1471,6 +1576,7 @@
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -1507,7 +1613,8 @@
       </c>
       <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n"/>
-      <c r="K4" s="5" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -1545,6 +1652,7 @@
       <c r="I5" s="4" t="n"/>
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -1582,6 +1690,7 @@
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -1621,6 +1730,7 @@
       </c>
       <c r="J7" s="4" t="n"/>
       <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -1658,6 +1768,7 @@
       <c r="I8" s="4" t="n"/>
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -1695,6 +1806,7 @@
       <c r="I9" s="4" t="n"/>
       <c r="J9" s="4" t="n"/>
       <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -1733,7 +1845,8 @@
         <v>3</v>
       </c>
       <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>테스트: 짧은 참석+최소 3게임 보장</t>
         </is>
@@ -1775,6 +1888,7 @@
       <c r="I11" s="4" t="n"/>
       <c r="J11" s="4" t="n"/>
       <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -1812,6 +1926,7 @@
       <c r="I12" s="4" t="n"/>
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1849,6 +1964,7 @@
       <c r="I13" s="4" t="n"/>
       <c r="J13" s="4" t="n"/>
       <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1886,6 +2002,7 @@
       <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1923,6 +2040,7 @@
       <c r="I15" s="4" t="n"/>
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1962,6 +2080,7 @@
         <v>3</v>
       </c>
       <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1999,6 +2118,7 @@
       <c r="I17" s="4" t="n"/>
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -2036,6 +2156,7 @@
       <c r="I18" s="4" t="n"/>
       <c r="J18" s="4" t="n"/>
       <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -2073,6 +2194,7 @@
       <c r="I19" s="4" t="n"/>
       <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -2110,6 +2232,7 @@
       <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -2147,6 +2270,7 @@
       <c r="I21" s="4" t="n"/>
       <c r="J21" s="4" t="n"/>
       <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -2184,6 +2308,7 @@
       <c r="I22" s="4" t="n"/>
       <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -2199,6 +2324,7 @@
       <c r="I23" s="4" t="n"/>
       <c r="J23" s="4" t="n"/>
       <c r="K23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -2214,6 +2340,7 @@
       <c r="I24" s="4" t="n"/>
       <c r="J24" s="4" t="n"/>
       <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -2229,6 +2356,7 @@
       <c r="I25" s="4" t="n"/>
       <c r="J25" s="4" t="n"/>
       <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -2244,6 +2372,7 @@
       <c r="I26" s="4" t="n"/>
       <c r="J26" s="4" t="n"/>
       <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -2259,6 +2388,7 @@
       <c r="I27" s="4" t="n"/>
       <c r="J27" s="4" t="n"/>
       <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -2274,6 +2404,7 @@
       <c r="I28" s="4" t="n"/>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -2289,6 +2420,7 @@
       <c r="I29" s="4" t="n"/>
       <c r="J29" s="4" t="n"/>
       <c r="K29" s="4" t="n"/>
+      <c r="L29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -2304,6 +2436,7 @@
       <c r="I30" s="4" t="n"/>
       <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -2319,6 +2452,7 @@
       <c r="I31" s="4" t="n"/>
       <c r="J31" s="4" t="n"/>
       <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
